--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N9_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.846963427493105</v>
+        <v>1.11263155696763</v>
       </c>
       <c r="D2" t="n">
-        <v>7.529772322792855</v>
+        <v>1.223588002453839</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
